--- a/output/pdf_financials_xlsx/ZRO.xlsx
+++ b/output/pdf_financials_xlsx/ZRO.xlsx
@@ -1907,10 +1907,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.608039</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.194627</v>
       </c>
     </row>
     <row r="93">
@@ -3155,7 +3155,11 @@
           <t>Warrant reserves 16</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ZRO.xlsx
+++ b/output/pdf_financials_xlsx/ZRO.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.063572</v>
+        <v>1.510389</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.434232</v>
+        <v>1.185594</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.716958</v>
+        <v>1.327547</v>
       </c>
     </row>
     <row r="11">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.005883</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.008529</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.026492</v>
       </c>
     </row>
     <row r="35">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.005883</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.008529</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.026492</v>
       </c>
     </row>
     <row r="37">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.031923</v>
+        <v>0.02604</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.016185</v>
+        <v>0.007656</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.026492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">

--- a/output/pdf_financials_xlsx/ZRO.xlsx
+++ b/output/pdf_financials_xlsx/ZRO.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>1.225056</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.321287</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.427643</v>
       </c>
     </row>
     <row r="65">
@@ -1501,10 +1501,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.393605</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.9085029999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2186,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.519656</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.54453</v>
       </c>
     </row>
     <row r="111">
@@ -3397,7 +3397,11 @@
           <t>Accretion expenses</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
